--- a/public/files/DATA/gem_data.xlsx
+++ b/public/files/DATA/gem_data.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B595B796-73CD-477B-A7BF-69A0307FD1FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DA6E53C-29F7-42C2-8959-469F5D31DEF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="27990" windowHeight="14415" xr2:uid="{38351AC5-F874-4B4A-BA41-290077078325}"/>
+    <workbookView xWindow="1320" yWindow="450" windowWidth="26205" windowHeight="14850" activeTab="1" xr2:uid="{38351AC5-F874-4B4A-BA41-290077078325}"/>
   </bookViews>
   <sheets>
     <sheet name="GEM" sheetId="9" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="10" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="93">
   <si>
     <t>ターコイズ</t>
     <phoneticPr fontId="1"/>
@@ -801,6 +802,29 @@
       <t>ハヤ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EXP10000</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宝石</t>
+    <rPh sb="0" eb="2">
+      <t>ホウセキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SR</t>
+  </si>
+  <si>
+    <t>EXP10000</t>
+  </si>
+  <si>
+    <t>SSR</t>
+  </si>
+  <si>
+    <t>MR</t>
   </si>
 </sst>
 </file>
@@ -902,7 +926,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -925,13 +949,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -979,6 +1016,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1862,4 +1905,459 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0037838C-F733-42E3-97B4-A53D198CD366}">
+  <dimension ref="A4:AD18"/>
+  <sheetFormatPr defaultColWidth="6.875" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="8" width="10.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2">
+        <v>4</v>
+      </c>
+      <c r="E4" s="2">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2">
+        <v>6</v>
+      </c>
+      <c r="G4" s="16">
+        <v>7</v>
+      </c>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="17"/>
+      <c r="U4" s="17"/>
+      <c r="V4" s="17"/>
+      <c r="W4" s="17"/>
+      <c r="X4" s="17"/>
+      <c r="Y4" s="17"/>
+      <c r="Z4" s="17"/>
+      <c r="AA4" s="17"/>
+      <c r="AB4" s="17"/>
+      <c r="AC4" s="17"/>
+      <c r="AD4" s="17"/>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="17"/>
+      <c r="T5" s="17"/>
+      <c r="U5" s="17"/>
+      <c r="V5" s="17"/>
+      <c r="W5" s="17"/>
+      <c r="X5" s="17"/>
+      <c r="Y5" s="17"/>
+      <c r="Z5" s="17"/>
+      <c r="AA5" s="17"/>
+      <c r="AB5" s="17"/>
+      <c r="AC5" s="17"/>
+      <c r="AD5" s="17"/>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="A7" s="2">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2">
+        <v>10</v>
+      </c>
+      <c r="D7" s="2">
+        <v>11</v>
+      </c>
+      <c r="E7" s="2">
+        <v>12</v>
+      </c>
+      <c r="F7" s="2">
+        <v>13</v>
+      </c>
+      <c r="G7" s="2">
+        <v>14</v>
+      </c>
+      <c r="H7" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="A10" s="2">
+        <v>16</v>
+      </c>
+      <c r="B10" s="2">
+        <f>A10+1</f>
+        <v>17</v>
+      </c>
+      <c r="C10" s="2">
+        <f t="shared" ref="C10" si="0">B10+1</f>
+        <v>18</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" ref="D10" si="1">C10+1</f>
+        <v>19</v>
+      </c>
+      <c r="E10" s="2">
+        <f t="shared" ref="E10" si="2">D10+1</f>
+        <v>20</v>
+      </c>
+      <c r="F10" s="2">
+        <f t="shared" ref="F10" si="3">E10+1</f>
+        <v>21</v>
+      </c>
+      <c r="G10" s="2">
+        <f t="shared" ref="G10" si="4">F10+1</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="A11" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="A13" s="2">
+        <v>23</v>
+      </c>
+      <c r="B13" s="2">
+        <v>24</v>
+      </c>
+      <c r="C13" s="2">
+        <v>25</v>
+      </c>
+      <c r="D13" s="2">
+        <v>26</v>
+      </c>
+      <c r="E13" s="2">
+        <v>27</v>
+      </c>
+      <c r="F13" s="2">
+        <v>28</v>
+      </c>
+      <c r="G13" s="2">
+        <v>29</v>
+      </c>
+      <c r="H13" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="A14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="A17" s="2">
+        <v>1</v>
+      </c>
+      <c r="B17" s="2">
+        <v>2</v>
+      </c>
+      <c r="C17" s="2">
+        <v>3</v>
+      </c>
+      <c r="D17" s="2">
+        <v>4</v>
+      </c>
+      <c r="E17" s="2">
+        <v>5</v>
+      </c>
+      <c r="F17" s="2">
+        <v>6</v>
+      </c>
+      <c r="G17" s="16">
+        <v>7</v>
+      </c>
+      <c r="H17" s="2">
+        <v>8</v>
+      </c>
+      <c r="I17" s="2">
+        <v>9</v>
+      </c>
+      <c r="J17" s="2">
+        <v>10</v>
+      </c>
+      <c r="K17" s="2">
+        <v>11</v>
+      </c>
+      <c r="L17" s="2">
+        <v>12</v>
+      </c>
+      <c r="M17" s="2">
+        <v>13</v>
+      </c>
+      <c r="N17" s="2">
+        <v>14</v>
+      </c>
+      <c r="O17" s="2">
+        <v>15</v>
+      </c>
+      <c r="P17" s="2">
+        <v>16</v>
+      </c>
+      <c r="Q17" s="2">
+        <f>P17+1</f>
+        <v>17</v>
+      </c>
+      <c r="R17" s="2">
+        <f t="shared" ref="R17" si="5">Q17+1</f>
+        <v>18</v>
+      </c>
+      <c r="S17" s="2">
+        <f t="shared" ref="S17" si="6">R17+1</f>
+        <v>19</v>
+      </c>
+      <c r="T17" s="2">
+        <f t="shared" ref="T17" si="7">S17+1</f>
+        <v>20</v>
+      </c>
+      <c r="U17" s="2">
+        <f t="shared" ref="U17" si="8">T17+1</f>
+        <v>21</v>
+      </c>
+      <c r="V17" s="2">
+        <f t="shared" ref="V17" si="9">U17+1</f>
+        <v>22</v>
+      </c>
+      <c r="W17" s="2">
+        <v>23</v>
+      </c>
+      <c r="X17" s="2">
+        <v>24</v>
+      </c>
+      <c r="Y17" s="2">
+        <v>25</v>
+      </c>
+      <c r="Z17" s="2">
+        <v>26</v>
+      </c>
+      <c r="AA17" s="2">
+        <v>27</v>
+      </c>
+      <c r="AB17" s="2">
+        <v>28</v>
+      </c>
+      <c r="AC17" s="2">
+        <v>29</v>
+      </c>
+      <c r="AD17" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="A18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="T18" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="U18" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="V18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="W18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="X18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA18" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB18" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD18" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>